--- a/data/SCHOOL GARDENS 2025.xlsx
+++ b/data/SCHOOL GARDENS 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamdatacollective.sharepoint.com/sites/InternalProjects2/Sector Healthcare/01_Knowledge sharing and building/02_Collective Events/ADC Collective Week/2024 - 2025/03 Project Folders/04 Project Folders/CW project - Amsterdam Schooltuinen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsterdamdatacollective-my.sharepoint.com/personal/thomas_b_adc-consulting_com/Documents/Documents/Collective Week/Code/Schooltuinen%20Amsterdam/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{5E507081-9C0C-4B8D-9DDC-F9F248963E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A485DEE-F705-4ED9-BD69-0E61BB6C4DC3}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{5E507081-9C0C-4B8D-9DDC-F9F248963E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{149AB719-FDA4-4621-8698-241237F5DAE1}"/>
   <bookViews>
-    <workbookView xWindow="14805" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{0137EE88-C707-4D8E-86E2-8EA2ECEDDBA0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0137EE88-C707-4D8E-86E2-8EA2ECEDDBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,16 +483,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD34B5F-63A4-40B6-96E6-BE462182540B}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,144 +509,222 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
         <v>520</v>
       </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="E2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
         <v>461</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
       <c r="E3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
         <v>450</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="E4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
       <c r="E5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6">
         <v>552</v>
       </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
       <c r="E6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
         <v>536</v>
       </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
         <v>575</v>
       </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
       <c r="E8">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
         <v>481</v>
       </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
       <c r="E9">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
         <v>558</v>
       </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
       <c r="E10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
         <v>887</v>
       </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
       <c r="E11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
         <v>540</v>
       </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
       <c r="E12">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
         <v>546</v>
       </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
       <c r="E13">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
         <v>558</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -661,6 +739,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A42C61A6A2258C40BDFECD0BFE7AB149" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2f2bd0a4d5f789eebc9e9c32900f24e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f414dda-f070-4b2c-a6a7-701907f758f3" xmlns:ns3="9701c0c3-e6e0-4347-a789-f10f63287cd9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a00c581b083e96fa0d5c8560d2b4ce04" ns2:_="" ns3:_="">
     <xsd:import namespace="5f414dda-f070-4b2c-a6a7-701907f758f3"/>
@@ -915,15 +1002,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -936,13 +1014,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687BE4FC-D9B3-454D-9140-5E29F5B38E68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{253E3F17-4DDE-421F-8DFF-3EA4EB145333}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{253E3F17-4DDE-421F-8DFF-3EA4EB145333}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{687BE4FC-D9B3-454D-9140-5E29F5B38E68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5f414dda-f070-4b2c-a6a7-701907f758f3"/>
+    <ds:schemaRef ds:uri="9701c0c3-e6e0-4347-a789-f10f63287cd9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07DC8DB6-C603-4411-B351-351E6A5C9C99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07DC8DB6-C603-4411-B351-351E6A5C9C99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5f414dda-f070-4b2c-a6a7-701907f758f3"/>
+    <ds:schemaRef ds:uri="9701c0c3-e6e0-4347-a789-f10f63287cd9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>